--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
@@ -681,7 +681,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,13 +691,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -712,20 +705,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1204,19 +1183,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1225,154 +1216,145 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1754,46 +1736,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:38">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -1802,186 +1784,186 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AK1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="8" t="s">
+      <c r="AL1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:38">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:38">
+      <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AH2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>74</v>
       </c>
     </row>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AH$1:$AH$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AJ$1:$AJ$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <r>
       <rPr>
@@ -165,6 +165,21 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单据子类型</t>
+    </r>
+  </si>
+  <si>
     <t>是否收取运费</t>
   </si>
   <si>
@@ -489,6 +504,9 @@
     <t>税率(%)</t>
   </si>
   <si>
+    <t>含税单价</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -554,6 +572,9 @@
     </r>
   </si>
   <si>
+    <t>客户PO号</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -575,6 +596,9 @@
     <t>{.sellerName}</t>
   </si>
   <si>
+    <t>{.transactionSubTypeName}</t>
+  </si>
+  <si>
     <t>{.isCollectShippingFee}</t>
   </si>
   <si>
@@ -656,6 +680,9 @@
     <t>{.taxRate}</t>
   </si>
   <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
     <t>{.isGift}</t>
   </si>
   <si>
@@ -663,6 +690,9 @@
   </si>
   <si>
     <t>{.isClose}</t>
+  </si>
+  <si>
+    <t>{.customerPO}</t>
   </si>
   <si>
     <t>{.detailRemark}</t>
@@ -1342,6 +1372,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1352,9 +1385,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1705,37 +1735,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
     <col min="3" max="3" width="35.375" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="8" width="25.625" customWidth="1"/>
-    <col min="9" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="21.125" customWidth="1"/>
-    <col min="13" max="14" width="20.625" customWidth="1"/>
-    <col min="15" max="18" width="15.625" customWidth="1"/>
-    <col min="19" max="23" width="20.625" customWidth="1"/>
-    <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="12.625" customWidth="1"/>
-    <col min="26" max="26" width="19.625" customWidth="1"/>
-    <col min="27" max="27" width="15.625" customWidth="1"/>
-    <col min="28" max="28" width="26.125" customWidth="1"/>
-    <col min="29" max="29" width="15.625" customWidth="1"/>
-    <col min="30" max="31" width="17.25" customWidth="1"/>
-    <col min="32" max="32" width="15.625" customWidth="1"/>
-    <col min="33" max="33" width="15.75" customWidth="1"/>
-    <col min="34" max="35" width="20.625" customWidth="1"/>
-    <col min="36" max="36" width="15.625" customWidth="1"/>
-    <col min="37" max="37" width="22" customWidth="1"/>
-    <col min="38" max="38" width="40" customWidth="1"/>
+    <col min="6" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="25.625" customWidth="1"/>
+    <col min="10" max="12" width="20.625" customWidth="1"/>
+    <col min="13" max="13" width="21.125" customWidth="1"/>
+    <col min="14" max="15" width="20.625" customWidth="1"/>
+    <col min="16" max="19" width="15.625" customWidth="1"/>
+    <col min="20" max="24" width="20.625" customWidth="1"/>
+    <col min="25" max="25" width="16.625" customWidth="1"/>
+    <col min="26" max="26" width="12.625" customWidth="1"/>
+    <col min="27" max="27" width="19.625" customWidth="1"/>
+    <col min="28" max="28" width="15.625" customWidth="1"/>
+    <col min="29" max="29" width="26.125" customWidth="1"/>
+    <col min="30" max="30" width="15.625" customWidth="1"/>
+    <col min="31" max="32" width="17.25" customWidth="1"/>
+    <col min="33" max="33" width="15.625" customWidth="1"/>
+    <col min="34" max="34" width="15.75" customWidth="1"/>
+    <col min="35" max="35" width="15.625" customWidth="1"/>
+    <col min="36" max="37" width="20.625" customWidth="1"/>
+    <col min="38" max="38" width="15.625" customWidth="1"/>
+    <col min="39" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:38">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1757,217 +1788,238 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AK1" s="7" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:38">
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
   <si>
     <r>
       <rPr>
@@ -166,6 +166,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -575,6 +582,9 @@
     <t>客户PO号</t>
   </si>
   <si>
+    <t>目的地</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -693,6 +703,9 @@
   </si>
   <si>
     <t>{.customerPO}</t>
+  </si>
+  <si>
+    <t>{.toCountry}</t>
   </si>
   <si>
     <t>{.detailRemark}</t>
@@ -1735,7 +1748,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1762,11 +1775,11 @@
     <col min="35" max="35" width="15.625" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
     <col min="38" max="38" width="15.625" customWidth="1"/>
-    <col min="39" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="40" customWidth="1"/>
+    <col min="39" max="41" width="22" customWidth="1"/>
+    <col min="42" max="42" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1885,135 +1898,141 @@
         <v>38</v>
       </c>
       <c r="AN1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AO1" s="5" t="s">
-        <v>39</v>
+      <c r="AP1" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <r>
       <rPr>
@@ -166,13 +166,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -582,9 +575,6 @@
     <t>客户PO号</t>
   </si>
   <si>
-    <t>目的地</t>
-  </si>
-  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -703,9 +693,6 @@
   </si>
   <si>
     <t>{.customerPO}</t>
-  </si>
-  <si>
-    <t>{.toCountry}</t>
   </si>
   <si>
     <t>{.detailRemark}</t>
@@ -1748,7 +1735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1775,11 +1762,11 @@
     <col min="35" max="35" width="15.625" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
     <col min="38" max="38" width="15.625" customWidth="1"/>
-    <col min="39" max="41" width="22" customWidth="1"/>
-    <col min="42" max="42" width="40" customWidth="1"/>
+    <col min="39" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1898,141 +1885,135 @@
         <v>38</v>
       </c>
       <c r="AN1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AP1" s="5" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+      <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExportError.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <r>
       <rPr>
@@ -557,28 +557,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否关闭</t>
-    </r>
-  </si>
-  <si>
     <t>客户PO号</t>
   </si>
   <si>
@@ -697,9 +675,6 @@
   </si>
   <si>
     <t>{.isReissue}</t>
-  </si>
-  <si>
-    <t>{.isClose}</t>
   </si>
   <si>
     <t>{.customerPO}</t>
@@ -1748,7 +1723,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1774,12 +1749,11 @@
     <col min="34" max="34" width="15.75" customWidth="1"/>
     <col min="35" max="35" width="15.625" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
-    <col min="38" max="38" width="15.625" customWidth="1"/>
-    <col min="39" max="41" width="22" customWidth="1"/>
-    <col min="42" max="42" width="40" customWidth="1"/>
+    <col min="38" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1898,141 +1872,135 @@
         <v>38</v>
       </c>
       <c r="AN1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AP1" s="5" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+      <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
